--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487485_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487485_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6768</v>
+        <v>2.5147</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.9428</v>
+        <v>0.1283</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6196</v>
+        <v>2.3864</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.8037</v>
+        <v>0.7477</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.173</v>
+        <v>1.0358</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6307</v>
+        <v>-0.2881</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3661</v>
+        <v>0.5936</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1793</v>
+        <v>0.6243</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8131</v>
+        <v>-0.0308</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4376</v>
+        <v>0.1541</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0062</v>
+        <v>0.4114</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4438</v>
+        <v>-0.2573</v>
       </c>
       <c r="P2" t="n">
-        <v>2.546</v>
+        <v>2.1543</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>4.7004</v>
+        <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4402</v>
+        <v>-0.3873</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0833</v>
+        <v>-0.4652</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3568</v>
+        <v>0.0779</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5057</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.5057</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4834</v>
+        <v>2.2372</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2194</v>
+        <v>1.1336</v>
       </c>
       <c r="F3" t="n">
-        <v>1.264</v>
+        <v>1.1036</v>
       </c>
       <c r="G3" t="n">
         <v>-0.044</v>
@@ -688,13 +688,13 @@
         <v>3.5253</v>
       </c>
       <c r="S3" t="n">
-        <v>0.54</v>
+        <v>0.2938</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8763</v>
+        <v>0.7904</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3363</v>
+        <v>-0.4967</v>
       </c>
       <c r="V3" t="n">
         <v>4.5335</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9285</v>
+        <v>1.1718</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2975</v>
+        <v>-2.3787</v>
       </c>
       <c r="F4" t="n">
-        <v>2.226</v>
+        <v>3.5504</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7477</v>
+        <v>-1.8037</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0358</v>
+        <v>-1.173</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2881</v>
+        <v>-0.6307</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5936</v>
+        <v>-0.3661</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6243</v>
+        <v>-1.1793</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0308</v>
+        <v>0.8131</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1541</v>
+        <v>-1.4376</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4114</v>
+        <v>0.0062</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2573</v>
+        <v>-1.4438</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1543</v>
+        <v>2.546</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1543</v>
+        <v>4.7004</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9735</v>
+        <v>0.9351</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.891</v>
+        <v>0.6475</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0825</v>
+        <v>0.2876</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.5057</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.5057</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0167</v>
+        <v>0.9365</v>
       </c>
       <c r="E5" t="n">
         <v>0.5293</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4874</v>
+        <v>0.4072</v>
       </c>
       <c r="G5" t="n">
         <v>0.1679</v>
@@ -844,13 +844,13 @@
         <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0653</v>
+        <v>-0.0149</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2435</v>
+        <v>0.1634</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. REY ARTIGAS</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.719</v>
+        <v>0.7662</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8681</v>
+        <v>-1.4551</v>
       </c>
       <c r="F6" t="n">
-        <v>1.587</v>
+        <v>2.2213</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.6504</v>
+        <v>0.155</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.9193</v>
+        <v>1.0293</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2688</v>
+        <v>-0.8743</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.8149</v>
+        <v>-0.3241</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.4015</v>
+        <v>0.9595</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5866</v>
+        <v>-1.2836</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8355</v>
+        <v>0.4791</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4822</v>
+        <v>0.0698</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3178</v>
+        <v>0.4093</v>
       </c>
       <c r="P6" t="n">
-        <v>2.546</v>
+        <v>0.5875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1751</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>3.7211</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8234</v>
+        <v>0.0237</v>
       </c>
       <c r="T6" t="n">
-        <v>2.122</v>
+        <v>-0.1517</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2986</v>
+        <v>0.1754</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.315</v>
+        <v>0.2991</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7192</v>
+        <v>-0.4321</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0342</v>
+        <v>0.7312</v>
       </c>
       <c r="G7" t="n">
-        <v>0.155</v>
+        <v>0.3349</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0293</v>
+        <v>0.7843</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8743</v>
+        <v>-0.4494</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3241</v>
+        <v>0.3694</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9595</v>
+        <v>0.4406</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2836</v>
+        <v>-0.0712</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4791</v>
+        <v>-0.0345</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0698</v>
+        <v>0.3437</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4093</v>
+        <v>-0.3782</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5668</v>
+        <v>2.1543</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4275</v>
+        <v>-0.4643</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4158</v>
+        <v>0.0982</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0117</v>
+        <v>-0.5625</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3346</v>
+        <v>0.2615</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7985</v>
+        <v>0.542</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4639</v>
+        <v>-0.2805</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3349</v>
+        <v>-1.6987</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7843</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4494</v>
+        <v>-1.1164</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3694</v>
+        <v>0.643</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4406</v>
+        <v>0.0271</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0712</v>
+        <v>0.6159</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0345</v>
+        <v>-2.3416</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3437</v>
+        <v>-0.6093</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3782</v>
+        <v>-1.7323</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9792</v>
+        <v>2.546</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1543</v>
+        <v>3.7211</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.098</v>
+        <v>0.2977</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2682</v>
+        <v>0.4658</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8299</v>
+        <v>-0.1681</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5507</v>
+        <v>-0.8837</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>R. REY ARTIGAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5887</v>
+        <v>-0.1626</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9388</v>
+        <v>-2.2843</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3501</v>
+        <v>2.1216</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4498</v>
+        <v>-2.6504</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2729</v>
+        <v>-3.9193</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1769</v>
+        <v>1.2688</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0404</v>
+        <v>-1.8149</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-4.4015</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0404</v>
+        <v>2.5866</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4093</v>
+        <v>-0.8355</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2729</v>
+        <v>0.4822</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1364</v>
+        <v>-1.3178</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9792</v>
+        <v>2.546</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.7211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0592</v>
+        <v>-0.0582</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.7058</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0592</v>
+        <v>-0.764</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>A. IGLESIAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6539</v>
+        <v>-0.3809</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2932</v>
+        <v>0.6207</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3607</v>
+        <v>-1.0016</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6987</v>
+        <v>0.6434</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-1.5795</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1164</v>
+        <v>2.2228</v>
       </c>
       <c r="J10" t="n">
-        <v>0.643</v>
+        <v>2.8537</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0271</v>
+        <v>-0.8337</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6159</v>
+        <v>3.6874</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3416</v>
+        <v>-2.2104</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6093</v>
+        <v>-0.7458</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7323</v>
+        <v>-1.4646</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.3917</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2.9377</v>
+      </c>
+      <c r="R10" t="n">
         <v>2.546</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-1.1751</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.7211</v>
-      </c>
       <c r="S10" t="n">
-        <v>-0.6176</v>
+        <v>0.3086</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3694</v>
+        <v>0.4293</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2482</v>
+        <v>-0.1207</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8837</v>
+        <v>-0.9412</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.492</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. IGLESIAS FERNANDEZ</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6718</v>
+        <v>-0.4596</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3566</v>
+        <v>-0.8365</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0284</v>
+        <v>0.3768</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6434</v>
+        <v>0.4498</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5795</v>
+        <v>0.2729</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2228</v>
+        <v>0.1769</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8537</v>
+        <v>0.0404</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8337</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3.6874</v>
+        <v>0.0404</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2104</v>
+        <v>0.4093</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7458</v>
+        <v>0.2729</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4646</v>
+        <v>0.1364</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3917</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>2.546</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0178</v>
+        <v>0.0698</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1653</v>
+        <v>0.1023</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1474</v>
+        <v>-0.0325</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9412</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6119</v>
+        <v>-1.014</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8748</v>
+        <v>-1.3037</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2629</v>
+        <v>0.2897</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3537</v>
@@ -1390,13 +1390,13 @@
         <v>1.5668</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2374</v>
+        <v>0.3604</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4158</v>
+        <v>0.1553</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1784</v>
+        <v>0.2051</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6083</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.278499999999998</v>
+        <v>6.169899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.627599999999999</v>
+        <v>-5.736499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>11.906</v>
+        <v>11.9061</v>
       </c>
       <c r="G13" t="n">
         <v>-5.0518</v>
@@ -1438,7 +1438,7 @@
         <v>-4.4475</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6044000000000002</v>
+        <v>-0.6044000000000004</v>
       </c>
       <c r="J13" t="n">
         <v>3.4955</v>
@@ -1450,7 +1450,7 @@
         <v>6.614799999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.5473</v>
+        <v>-8.547300000000002</v>
       </c>
       <c r="N13" t="n">
         <v>-1.3282</v>
@@ -1468,10 +1468,10 @@
         <v>26.4395</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4735000000000002</v>
+        <v>1.3644</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7085</v>
+        <v>2.5995</v>
       </c>
       <c r="U13" t="n">
         <v>-1.2351</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4392</v>
+        <v>7.6605</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1847</v>
+        <v>5.0823</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2546</v>
+        <v>2.5781</v>
       </c>
       <c r="G14" t="n">
         <v>6.8062</v>
@@ -1546,13 +1546,13 @@
         <v>2.3502</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0301</v>
+        <v>0.2513</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1764</v>
+        <v>0.0741</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1464</v>
+        <v>0.1772</v>
       </c>
       <c r="V14" t="n">
         <v>0.2113</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1639</v>
+        <v>7.1684</v>
       </c>
       <c r="E15" t="n">
-        <v>6.4392</v>
+        <v>6.3368</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7247</v>
+        <v>0.8316</v>
       </c>
       <c r="G15" t="n">
         <v>6.0954</v>
@@ -1624,13 +1624,13 @@
         <v>2.7419</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2016</v>
+        <v>-0.197</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4317</v>
+        <v>0.3293</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6333</v>
+        <v>-0.5264</v>
       </c>
       <c r="V15" t="n">
         <v>0.4866</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3608</v>
+        <v>1.2467</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8069</v>
+        <v>1.3185</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4461</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>2.3332</v>
@@ -1702,13 +1702,13 @@
         <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3173</v>
+        <v>-0.4314</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9504</v>
+        <v>-0.4388</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3669</v>
+        <v>0.0074</v>
       </c>
       <c r="V16" t="n">
         <v>-2.2219</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0941</v>
+        <v>0.1162</v>
       </c>
       <c r="E17" t="n">
-        <v>0.095</v>
+        <v>0.1973</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.001</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.6359</v>
@@ -1780,13 +1780,13 @@
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0718</v>
+        <v>0.094</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4752</v>
+        <v>-0.3729</v>
       </c>
       <c r="U17" t="n">
-        <v>0.547</v>
+        <v>0.4668</v>
       </c>
       <c r="V17" t="n">
         <v>-1.6136</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>A. NONGO N'SALA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9745</v>
+        <v>-0.8528</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.4275</v>
+        <v>-0.6783</v>
       </c>
       <c r="F18" t="n">
-        <v>2.453</v>
+        <v>-0.1745</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.361</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6847</v>
+        <v>0.2256</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3237</v>
+        <v>-0.9499</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.514</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.1711</v>
+        <v>0.0204</v>
       </c>
       <c r="L18" t="n">
-        <v>1.657</v>
+        <v>-0.6822</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8469</v>
+        <v>-0.0625</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4864</v>
+        <v>0.2052</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.3333</v>
+        <v>-0.2677</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.1336</v>
+        <v>0.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.8755</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7419</v>
+        <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9331</v>
+        <v>-0.2448</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2535</v>
+        <v>-0.0165</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6797</v>
+        <v>-0.2283</v>
       </c>
       <c r="V18" t="n">
-        <v>2.5869</v>
+        <v>-0.2754</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7086</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1217</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. NONGO N'SALA</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1183</v>
+        <v>-1.3819</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7806</v>
+        <v>-3.2228</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3377</v>
+        <v>1.841</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-1.361</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2256</v>
+        <v>-1.6847</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9499</v>
+        <v>0.3237</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.514</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0204</v>
+        <v>-2.1711</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6822</v>
+        <v>1.657</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0625</v>
+        <v>-0.8469</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2052</v>
+        <v>0.4864</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2677</v>
+        <v>-1.3333</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3917</v>
+        <v>-3.1336</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-5.8755</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3917</v>
+        <v>2.7419</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5103</v>
+        <v>0.5258</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1188</v>
+        <v>0.4581</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3915</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2754</v>
+        <v>2.5869</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5468</v>
+        <v>-2.5394</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5095</v>
+        <v>-3.6118</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9627</v>
+        <v>1.0724</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6268</v>
@@ -2014,13 +2014,13 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2551</v>
+        <v>0.2625</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0882</v>
+        <v>-0.0141</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1669</v>
+        <v>0.2766</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3067</v>
+        <v>-3.0707</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.595</v>
+        <v>-2.4927</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7117</v>
+        <v>-0.578</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1133</v>
@@ -2092,13 +2092,13 @@
         <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1726</v>
+        <v>0.0634</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2841</v>
+        <v>0.3864</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4567</v>
+        <v>-0.323</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6083</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5932</v>
+        <v>-3.5978</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.636</v>
+        <v>-5.5337</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0428</v>
+        <v>1.9359</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8825</v>
@@ -2170,13 +2170,13 @@
         <v>0.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.243</v>
+        <v>-0.2476</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4158</v>
+        <v>-0.3135</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1728</v>
+        <v>0.0659</v>
       </c>
       <c r="V22" t="n">
         <v>0.6659</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. JUAN SEVILLANO</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2003</v>
+        <v>-4.0464</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3381</v>
+        <v>-3.8382</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1378</v>
+        <v>-0.2082</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.229</v>
+        <v>-1.8819</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1119</v>
+        <v>-1.2249</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1172</v>
+        <v>-0.657</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5728</v>
+        <v>-0.3341</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2535</v>
+        <v>-0.3437</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3192</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6563</v>
+        <v>-1.5479</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1416</v>
+        <v>-0.8812</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.6667</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.1336</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.8962</v>
+        <v>-3.917</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1623</v>
+        <v>0.0694</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8556</v>
+        <v>0.4129</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6932</v>
+        <v>-0.3435</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-0.2754</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>M. JUAN SEVILLANO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5968</v>
+        <v>-5.2992</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1452</v>
+        <v>-5.4638</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4516</v>
+        <v>0.1645</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8819</v>
+        <v>-2.229</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2249</v>
+        <v>-0.1119</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.657</v>
+        <v>-2.1172</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3341</v>
+        <v>-1.5728</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3437</v>
+        <v>-0.2535</v>
       </c>
       <c r="L24" t="n">
-        <v>0.009599999999999999</v>
+        <v>-1.3192</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5479</v>
+        <v>-0.6563</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8812</v>
+        <v>0.1416</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6667</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.9585</v>
+        <v>-3.1336</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.917</v>
+        <v>-4.8962</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9585</v>
+        <v>1.7626</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.481</v>
+        <v>0.0634</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1059</v>
+        <v>0.7299</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5868</v>
+        <v>-0.6665</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X24" t="n">
         <v>-0.2754</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.278600000000001</v>
+        <v>-4.596399999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.9061</v>
+        <v>-11.9064</v>
       </c>
       <c r="F25" t="n">
-        <v>6.6275</v>
+        <v>7.309800000000001</v>
       </c>
       <c r="G25" t="n">
         <v>5.051899999999999</v>
@@ -2380,13 +2380,13 @@
         <v>8.547199999999997</v>
       </c>
       <c r="K25" t="n">
-        <v>1.3279</v>
+        <v>1.327899999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>7.2191</v>
+        <v>7.219100000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.495200000000001</v>
+        <v>-3.4952</v>
       </c>
       <c r="N25" t="n">
         <v>3.1195</v>
@@ -2395,7 +2395,7 @@
         <v>-6.614800000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.813299999999998</v>
+        <v>-8.8133</v>
       </c>
       <c r="Q25" t="n">
         <v>-26.4396</v>
@@ -2404,13 +2404,13 @@
         <v>17.6264</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4733999999999995</v>
+        <v>0.209</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2352</v>
+        <v>1.2349</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7084</v>
+        <v>-1.0262</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0439</v>
